--- a/output/2026-09-20_08_Croazia_Vukovarsko-srijemska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-20_08_Croazia_Vukovarsko-srijemska_Componentistica_Ventilazione_industriale.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rivenditore/grossista di materiali e attrezzature per riscaldamento e climatizzazione (residenziale e industriale), sanitari ed energie rinnovabili; attivo dal 1993 come fornitore di installatori e clienti finali in tutta la contea. Copertura specifica di componentistica per ventilazione industriale non confermata, generalista HVAC/termoidraulico. Esistenza e attività confermate tramite emajstor.hr, epoduzetnici.hr e sito ufficiale (fetch diretto bloccato da proxy, verificato via ricerca web); telefono/email coerenti col sito ma non riscontrati testualmente negli snippet.</t>
+          <t>Rivenditore/grossista di materiali e attrezzature per riscaldamento e climatizzazione (residenziale e industriale), sanitari ed energie rinnovabili; attivo dal 1993 come fornitore di installatori e clienti finali in tutta la contea. Copertura specifica di componentistica per ventilazione industriale non confermata, generalista HVAC/termoidraulico. Esistenza e attività confermate tramite emajstor.hr, epoduzetnici.hr e sito ufficiale (fetch diretto bloccato da proxy, verificato via ricerca web); telefono/email coerenti col sito ma non riscontrati testualmente negli snippet. [DUPLICATO — vedi anche: 2026-09-20_07_Croazia_Vukovarsko-srijemska_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
